--- a/stories/arbres/ATOM-FAM.SEC.002-04.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Thaïs est au marché avec papa. Elle sent le pain chaud. Un adulte parle tout bas. Il dit : c'est notre secret. Thaïs sent son ventre. C'est serré. C'est un malaise. Thaïs a peur. Thaïs marche vers papa. Elle prend sa main. Thaïs dit : papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Papa dit : merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Thaïs le dit aussi à maman. Maman écoute. Thaïs se sent plus légère.</t>
+          <t>Thaïs est au marché avec papa. Elle sent le pain chaud. Un adulte parle tout bas. C'est notre secret. Thaïs sent son ventre. C'est serré. C'est un malaise. Thaïs a peur. Thaïs marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Thaïs le dit aussi à maman. Maman écoute. Thaïs se sent plus légère.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Thaïs est au marché avec papa. Elle sent le pain chaud. Un adulte parle tout bas.
+narrateur|C'est notre secret.
+narrateur|Thaïs sent son ventre. C'est serré. C'est un malaise. Thaïs a peur. Thaïs marche vers papa. Elle prend sa main.
+enfant-m|Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute.
+papa|Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Thaïs le dit aussi à maman. Maman écoute.
+narrateur|Thaïs se sent plus légère.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Thaïs a peur. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Thaïs a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1835,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Thaïs s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2002,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2042,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-04.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Thaïs se sent plus légère.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Thaïs a peur. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1680,7 @@
           <t>narrateur|Thaïs a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1840,6 +1848,7 @@
           <t>narrateur|Thaïs s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2007,6 +2016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2049,6 +2059,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2250,6 +2274,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.SEC.002-04.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thaïs raconte ce qui fait peur</t>
+          <t>Victorina raconte près du pain</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un sac en papier froisse près du pain chaud. Victorina raconte à papa, puis à maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Thaïs est au marché avec papa. Elle sent le pain chaud. Un adulte parle tout bas. C'est notre secret. Thaïs sent son ventre. C'est serré. C'est un malaise. Thaïs a peur. Thaïs marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Thaïs le dit aussi à maman. Maman écoute. Thaïs se sent plus légère.</t>
+          <t>Un sac en papier froisse. Il fait un petit chut. De la farine dort sur une manche. Elle est blanche et douce. Le pain chaud sent fort. La croûte craque un peu. Le four du stand brille. Victorina, tu sens le pain ? Il est chaud, papa. Oui. En ce moment, Victorina est au marché. Elle tient le sac en papier. Le sac est un peu rêche. On le porte ensemble. Il est lourd un peu. Je t'aide. Une voix d'adulte parle tout bas. Victorina sent son ventre. Le ventre est serré. C'est un malaise. Victorina a peur. Elle tend le sac à papa. Elle marche vers lui. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Tu tiens ma main ? Oui, Victorina. Bravo. Tu as fait du bon travail. Papa tient sa main. La main de papa est chaude. Le sac froisse encore un peu. Plus tard, ils rentrent à la maison. Le pain sent encore le four. Maman ouvre la fenêtre. Ça sent le pain. Victorina a quelque chose à dire. Victorina marche vers maman. Maman, j'ai eu peur au marché. Mon ventre était serré. J'ai raconté à papa. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je me sens plus légère. Bravo, Victorina. Tu as fait du bon travail. Victorina s'assoit près de maman. Papa pose le sac. Un peu de farine tombe.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Thaïs est au marché avec papa. Elle sent le pain chaud. Un adulte parle tout bas.
-narrateur|C'est notre secret.
-narrateur|Thaïs sent son ventre. C'est serré. C'est un malaise. Thaïs a peur. Thaïs marche vers papa. Elle prend sa main.
-enfant-m|Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute.
-papa|Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Thaïs le dit aussi à maman. Maman écoute.
-narrateur|Thaïs se sent plus légère.</t>
+          <t>narrateur|Un sac en papier froisse.
+narrateur|Il fait un petit chut.
+narrateur|De la farine dort sur une manche.
+narrateur|Elle est blanche et douce.
+narrateur|Le pain chaud sent fort.
+narrateur|La croûte craque un peu.
+narrateur|Le four du stand brille.
+papa|Victorina, tu sens le pain ?
+enfant-f|Il est chaud, papa.
+papa|Oui.
+narrateur|En ce moment, Victorina est au marché.
+narrateur|Elle tient le sac en papier.
+narrateur|Le sac est un peu rêche.
+papa|On le porte ensemble.
+enfant-f|Il est lourd un peu.
+papa|Je t'aide.
+narrateur|Une voix d'adulte parle tout bas.
+narrateur|Victorina sent son ventre.
+narrateur|Le ventre est serré.
+narrateur|C'est un malaise.
+narrateur|Victorina a peur.
+narrateur|Elle tend le sac à papa.
+narrateur|Elle marche vers lui.
+narrateur|Elle prend sa main.
+enfant-f|Papa, un adulte a parlé d'un secret.
+enfant-f|Mon ventre est serré.
+enfant-f|J'ai peur.
+papa|Merci de raconter.
+papa|Tu as le droit de le dire.
+papa|Ce qui fait peur se raconte.
+papa|On va raconter à papa ou maman.
+papa|Je reste tout près.
+enfant-f|Tu tiens ma main ?
+papa|Oui, Victorina.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Papa tient sa main.
+narrateur|La main de papa est chaude.
+narrateur|Le sac froisse encore un peu.
+narrateur|Plus tard, ils rentrent à la maison.
+narrateur|Le pain sent encore le four.
+narrateur|Maman ouvre la fenêtre.
+maman|Ça sent le pain.
+papa|Victorina a quelque chose à dire.
+narrateur|Victorina marche vers maman.
+enfant-f|Maman, j'ai eu peur au marché.
+enfant-f|Mon ventre était serré.
+enfant-f|J'ai raconté à papa.
+maman|Merci de raconter.
+maman|Tu as le droit de le dire.
+maman|Ce qui fait peur se raconte.
+maman|On va raconter à papa ou maman.
+enfant-f|Je me sens plus légère.
+maman|Bravo, Victorina.
+maman|Tu as fait du bon travail.
+narrateur|Victorina s'assoit près de maman.
+narrateur|Papa pose le sac.
+narrateur|Un peu de farine tombe.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1345,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Thaïs a peur. Que fait-elle ?</t>
+          <t>Victorina a peur. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1505,7 +1569,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Thaïs a peur. Que fait-elle ?</t>
+          <t>narrateur|Victorina a peur.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1533,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Thaïs a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+          <t>Victorina a senti le malaise. Elle a marché vers papa. Elle a raconté. Tu as raconté au marché ? Oui. Puis à maman aussi. Bravo. Ce qui fait peur se raconte. On va raconter à papa ou maman. Le sac en papier se tait. Le pain reste chaud.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1677,7 +1742,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Thaïs a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+          <t>narrateur|Victorina a senti le malaise.
+narrateur|Elle a marché vers papa.
+narrateur|Elle a raconté.
+papa|Tu as raconté au marché ?
+enfant-f|Oui.
+maman|Puis à maman aussi.
+maman|Bravo.
+papa|Ce qui fait peur se raconte.
+papa|On va raconter à papa ou maman.
+narrateur|Le sac en papier se tait.
+narrateur|Le pain reste chaud.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1705,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Thaïs s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+          <t>Victorina s'assoit près de maman. Papa coupe un bout de pain. La croûte craque. Tu es là, avec nous. Oui. Le pain est encore chaud. Tu as raconté. C'est du bon travail. Je suis près de toi. Un peu de farine brille au soleil. On reste encore un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1845,7 +1920,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Thaïs s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+          <t>narrateur|Victorina s'assoit près de maman.
+narrateur|Papa coupe un bout de pain.
+maman|La croûte craque.
+papa|Tu es là, avec nous.
+enfant-f|Oui.
+enfant-f|Le pain est encore chaud.
+maman|Tu as raconté.
+maman|C'est du bon travail.
+papa|Je suis près de toi.
+narrateur|Un peu de farine brille au soleil.
+maman|On reste encore un peu.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1873,7 +1958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac en papier dort sur la table. J'ai raconté. Bravo, Victorina. On t'écoute. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2013,7 +2098,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le sac en papier dort sur la table.
+enfant-f|J'ai raconté.
+papa|Bravo, Victorina.
+maman|On t'écoute.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2035,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2073,6 +2162,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-04.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un sac en papier froisse. Il fait un petit chut. De la farine dort sur une manche. Elle est blanche et douce. Le pain chaud sent fort. La croûte craque un peu. Le four du stand brille. Victorina, tu sens le pain ? Il est chaud, papa. Oui. En ce moment, Victorina est au marché. Elle tient le sac en papier. Le sac est un peu rêche. On le porte ensemble. Il est lourd un peu. Je t'aide. Une voix d'adulte parle tout bas. Victorina sent son ventre. Le ventre est serré. C'est un malaise. Victorina a peur. Elle tend le sac à papa. Elle marche vers lui. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Tu tiens ma main ? Oui, Victorina. Bravo. Tu as fait du bon travail. Papa tient sa main. La main de papa est chaude. Le sac froisse encore un peu. Plus tard, ils rentrent à la maison. Le pain sent encore le four. Maman ouvre la fenêtre. Ça sent le pain. Victorina a quelque chose à dire. Victorina marche vers maman. Maman, j'ai eu peur au marché. Mon ventre était serré. J'ai raconté à papa. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je me sens plus légère. Bravo, Victorina. Tu as fait du bon travail. Victorina s'assoit près de maman. Papa pose le sac. Un peu de farine tombe.</t>
+          <t>Un sac en papier froisse. Il fait un petit chut. De la farine dort sur une manche. Elle est blanche et douce. Le pain chaud sent fort. La croûte craque un peu. Le four du stand brille. Victorina, tu sens le pain ? Il est chaud, papa. Oui. En ce moment, Victorina est au marché. Elle tient le sac en papier. Le sac est un peu rêche. On le porte ensemble. Il est lourd un peu. Je t'aide. Une voix d'adulte parle tout bas. Victorina sent son ventre. Le ventre est serré. C'est un malaise. Victorina a peur. Elle tend le sac à papa. Elle marche vers lui. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Tu tiens ma main ? Oui, Victorina. Bravo. Papa tient sa main. La main de papa est chaude. Le sac froisse encore un peu. Plus tard, ils rentrent à la maison. Le pain sent encore le four. Maman ouvre la fenêtre. Ça sent le pain. Victorina a quelque chose à dire. Victorina marche vers maman. Maman, j'ai eu peur au marché. Mon ventre était serré. J'ai raconté à papa. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je me sens plus légère. Bravo, Victorina. Victorina s'assoit près de maman. Papa pose le sac. Un peu de farine tombe.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Thaïs est au marché avec papa. Elle sent le pain chaud. Un adulte parle tout bas. Il dit : c'est notre secret. Thaïs sent son ventre. C'est serré. C'est un malaise. Thaïs a &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Thaïs marche vers papa. Elle prend sa main. Thaïs dit : papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Papa dit : merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Plus tard, à la maison, Thaïs le dit aussi à maman. Maman écoute. Thaïs se sent plus légère.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un sac en papier froisse. Il fait un petit chut. De la farine dort sur une manche. Elle est blanche et douce. Le pain chaud sent fort. La croûte craque un peu. Le four du stand brille. Victorina, tu sens le pain ? Il est chaud, papa. Oui. En ce moment, Victorina est au marché. Elle tient le sac en papier. Le sac est un peu rêche. On le porte ensemble. Il est lourd un peu. Je t'aide. Une voix d'adulte parle tout bas. Victorina sent son ventre. Le ventre est serré. C'est un malaise. Victorina a peur. Elle tend le sac à papa. Elle marche vers lui. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Tu tiens ma main ? Oui, Victorina. Bravo. Papa tient sa main. La main de papa est chaude. Le sac froisse encore un peu. Plus tard, ils rentrent à la maison. Le pain sent encore le four. Maman ouvre la fenêtre. Ça sent le pain. Victorina a quelque chose à dire. Victorina marche vers maman. Maman, j'ai eu peur au marché. Mon ventre était serré. J'ai raconté à papa. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je me sens plus légère. Bravo, Victorina. Victorina s'assoit près de maman. Papa pose le sac. Un peu de farine tombe.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1359,7 +1359,6 @@
 enfant-f|Tu tiens ma main ?
 papa|Oui, Victorina.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Papa tient sa main.
 narrateur|La main de papa est chaude.
 narrateur|Le sac froisse encore un peu.
@@ -1378,13 +1377,11 @@
 maman|On va raconter à papa ou maman.
 enfant-f|Je me sens plus légère.
 maman|Bravo, Victorina.
-maman|Tu as fait du bon travail.
 narrateur|Victorina s'assoit près de maman.
 narrateur|Papa pose le sac.
 narrateur|Un peu de farine tombe.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1414,7 +1411,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Thaïs a &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a peur. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1573,7 +1570,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1603,7 +1599,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Thaïs a senti le malaise. Elle a marché vers papa. Elle a raconté. Papa et maman écoutent. Ce qui fait &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt; se raconte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a senti le malaise. Elle a marché vers papa. Elle a raconté. Tu as raconté au marché ? Oui. Puis à maman aussi. Bravo. Ce qui fait peur se raconte. On va raconter à papa ou maman. Le sac en papier se tait. Le pain reste chaud.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1755,7 +1751,6 @@
 narrateur|Le pain reste chaud.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1780,12 +1775,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Victorina s'assoit près de maman. Papa coupe un bout de pain. La croûte craque. Tu es là, avec nous. Oui. Le pain est encore chaud. Tu as raconté. C'est du bon travail. Je suis près de toi. Un peu de farine brille au soleil. On reste encore un peu.</t>
+          <t>Victorina s'assoit près de maman. Papa coupe un bout de pain. La croûte craque. Tu es là, avec nous. Oui. Le pain est encore chaud. Tu as raconté. Je suis près de toi. Un peu de farine brille au soleil. On reste encore un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Thaïs s'assoit près de maman. Papa est là aussi. Sa &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; est chaude.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina s'assoit près de maman. Papa coupe un bout de pain. La croûte craque. Tu es là, avec nous. Oui. Le pain est encore chaud. Tu as raconté. Je suis près de toi. Un peu de farine brille au soleil. On reste encore un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1927,13 +1922,11 @@
 enfant-f|Oui.
 enfant-f|Le pain est encore chaud.
 maman|Tu as raconté.
-maman|C'est du bon travail.
 papa|Je suis près de toi.
 narrateur|Un peu de farine brille au soleil.
 maman|On reste encore un peu.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1958,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le sac en papier dort sur la table. J'ai raconté. Bravo, Victorina. On t'écoute. L'histoire est finie.</t>
+          <t>Le sac en papier dort sur la table. J'ai raconté. Bravo, Victorina. On t'écoute.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le sac en papier dort sur la table. J'ai raconté. Bravo, Victorina. On t'écoute.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2101,11 +2094,9 @@
           <t>narrateur|Le sac en papier dort sur la table.
 enfant-f|J'ai raconté.
 papa|Bravo, Victorina.
-maman|On t'écoute.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|On t'écoute.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2124,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2169,6 +2160,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-04.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>marché</t>
+          <t>marché, stand du pain, puis maison</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thaïs, papa, maman</t>
+          <t>Victorina, papa, maman</t>
         </is>
       </c>
     </row>
